--- a/site/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/site/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>

--- a/site/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/site/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/site/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/site/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg?docket=2024-NC-003110</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake</t>
+          <t>https://www.nccourts.gov/locations/wake/wake-county-clerk-of-superior-court?docket=2024-NC-001420</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg?docket=2024-NC-003450</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake</t>
+          <t>https://www.nccourts.gov/locations/wake/wake-county-clerk-of-superior-court?docket=2024-NC-001890</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/durham</t>
+          <t>https://www.nccourts.gov/locations/durham?docket=2024-NC-002100</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>

--- a/site/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/site/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg?docket=2024-NC-003110</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake/wake-county-clerk-of-superior-court?docket=2024-NC-001420</t>
+          <t>https://www.nccourts.gov/locations/wake</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg?docket=2024-NC-003450</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake/wake-county-clerk-of-superior-court?docket=2024-NC-001890</t>
+          <t>https://www.nccourts.gov/locations/wake</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/durham?docket=2024-NC-002100</t>
+          <t>https://www.nccourts.gov/locations/durham</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/site/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/site/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg-county?docket=2024-NC-003110</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake</t>
+          <t>https://www.nccourts.gov/locations/wake-county?docket=2024-NC-001420</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg-county?docket=2024-NC-003450</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake</t>
+          <t>https://www.nccourts.gov/locations/wake-county?docket=2024-NC-001890</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/durham</t>
+          <t>https://www.nccourts.gov/locations/durham-county?docket=2024-NC-002100</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>

--- a/site/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/site/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>

--- a/site/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/site/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>

--- a/site/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/site/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>

--- a/site/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/site/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>

--- a/site/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/site/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>

--- a/site/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/site/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
